--- a/NECP Scenario/Results/Regional Results/THIRA_Generation.xlsx
+++ b/NECP Scenario/Results/Regional Results/THIRA_Generation.xlsx
@@ -563,25 +563,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3.892749077813031E-08</v>
+        <v>5.749146939689347E-08</v>
       </c>
       <c r="C3">
-        <v>2.260811574527639E-08</v>
+        <v>3.338595076362562E-08</v>
       </c>
       <c r="D3">
-        <v>3.709418107724458E-07</v>
+        <v>7.03277205663201E-07</v>
       </c>
       <c r="E3">
-        <v>1.076742515243804E-06</v>
+        <v>0.01528780081744513</v>
       </c>
       <c r="F3">
-        <v>0.05147782845125809</v>
+        <v>0.1136746289115858</v>
       </c>
       <c r="G3">
-        <v>0.1470104871332872</v>
+        <v>0.2258473032954134</v>
       </c>
       <c r="H3">
-        <v>0.2554986221239938</v>
+        <v>0.3493492899871752</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -589,25 +589,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3.308836716363262E-08</v>
+        <v>4.886774898915951E-08</v>
       </c>
       <c r="C4">
-        <v>1.921689838570677E-08</v>
+        <v>2.837805815088185E-08</v>
       </c>
       <c r="D4">
-        <v>3.153005391588009E-07</v>
+        <v>5.97785624815521E-07</v>
       </c>
       <c r="E4">
-        <v>9.152311379594557E-07</v>
+        <v>0.01299463069482662</v>
       </c>
       <c r="F4">
-        <v>0.04375615418357275</v>
+        <v>0.09662343457485494</v>
       </c>
       <c r="G4">
-        <v>0.124958914063331</v>
+        <v>0.1919702078010923</v>
       </c>
       <c r="H4">
-        <v>0.217173828805398</v>
+        <v>0.2969468964891022</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -849,25 +849,25 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.2586408753278979</v>
+        <v>0.2586408767067563</v>
       </c>
       <c r="C14">
-        <v>0.2924943632462104</v>
+        <v>0.2924943638582715</v>
       </c>
       <c r="D14">
-        <v>0.321443089063616</v>
+        <v>0.2779782748438619</v>
       </c>
       <c r="E14">
-        <v>0.3400883742644834</v>
+        <v>0.3400883913037764</v>
       </c>
       <c r="F14">
-        <v>0.420620980172407</v>
+        <v>0.420621009857115</v>
       </c>
       <c r="G14">
-        <v>0.5064171636456922</v>
+        <v>0.506417202143703</v>
       </c>
       <c r="H14">
-        <v>0.644323090982801</v>
+        <v>0.6443233176832817</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1213,25 +1213,25 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>0.7167307794804207</v>
+        <v>0.7167307948570844</v>
       </c>
       <c r="C28">
-        <v>0.8106914692692877</v>
+        <v>0.8106914771247069</v>
       </c>
       <c r="D28">
-        <v>3.520776338588995E-08</v>
+        <v>5.225853496548401E-08</v>
       </c>
       <c r="E28">
-        <v>4.393212605714527E-08</v>
+        <v>6.475259823917893E-08</v>
       </c>
       <c r="F28">
-        <v>4.291161409867828E-08</v>
+        <v>6.341051883291396E-08</v>
       </c>
       <c r="G28">
-        <v>0.001798342173906812</v>
+        <v>0.001798365660871914</v>
       </c>
       <c r="H28">
-        <v>0.002975609022491737</v>
+        <v>0.002186973603731329</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1239,25 +1239,25 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>0.2635039630315684</v>
+        <v>0.2635039686786215</v>
       </c>
       <c r="C29">
-        <v>0.2980483342834984</v>
+        <v>0.2980483371683212</v>
       </c>
       <c r="D29">
-        <v>1.29342127743808E-08</v>
+        <v>1.919819670967629E-08</v>
       </c>
       <c r="E29">
-        <v>1.61370848730698E-08</v>
+        <v>2.37847899476099E-08</v>
       </c>
       <c r="F29">
-        <v>1.575510949653326E-08</v>
+        <v>2.328135824720478E-08</v>
       </c>
       <c r="G29">
-        <v>0.0006611551797986741</v>
+        <v>0.000661163799846292</v>
       </c>
       <c r="H29">
-        <v>0.001093973716118984</v>
+        <v>0.0008040341338239217</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1271,19 +1271,19 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>0.02926903094058477</v>
+        <v>0.02184627395811863</v>
       </c>
       <c r="E30">
-        <v>0.05417871405908163</v>
+        <v>0.06229391213922952</v>
       </c>
       <c r="F30">
-        <v>0.07238334200331739</v>
+        <v>0.07238253282746265</v>
       </c>
       <c r="G30">
-        <v>0.07238278491846432</v>
+        <v>0.0723816435038255</v>
       </c>
       <c r="H30">
-        <v>0.0723728910058833</v>
+        <v>0.07236667663871284</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1291,25 +1291,25 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.0004153033807558816</v>
+        <v>0.0004153019417810749</v>
       </c>
       <c r="C31">
-        <v>0.0004153050914861885</v>
+        <v>0.0004153044562837991</v>
       </c>
       <c r="D31">
-        <v>0.0004146956731890343</v>
+        <v>0.000414487005615034</v>
       </c>
       <c r="E31">
-        <v>0.0004142919258202113</v>
+        <v>0.0004138188587893606</v>
       </c>
       <c r="F31">
-        <v>0.0004137530678131969</v>
+        <v>0.0004132649289347785</v>
       </c>
       <c r="G31">
-        <v>0.0004132973329716934</v>
+        <v>0.0004126902625887633</v>
       </c>
       <c r="H31">
-        <v>0.0004072188537124695</v>
+        <v>0.0004049591565453284</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1323,19 +1323,19 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>9.050422968859299E-07</v>
+        <v>0.04346572489863488</v>
       </c>
       <c r="E32">
-        <v>0.04346572313452744</v>
+        <v>0.04346571457545431</v>
       </c>
       <c r="F32">
-        <v>0.04346571029270446</v>
+        <v>0.04346569509031719</v>
       </c>
       <c r="G32">
-        <v>0.04346569199297121</v>
+        <v>0.04346567205003248</v>
       </c>
       <c r="H32">
-        <v>0.04346545302147347</v>
+        <v>0.04346533121156037</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1343,25 +1343,25 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.001212691908966848</v>
+        <v>0.001212690546524041</v>
       </c>
       <c r="C33">
-        <v>0.001212693510166043</v>
+        <v>0.00121269290687446</v>
       </c>
       <c r="D33">
-        <v>0.00121268271652284</v>
+        <v>0.001212677092631281</v>
       </c>
       <c r="E33">
-        <v>0.001212674048793945</v>
+        <v>0.001212665587307799</v>
       </c>
       <c r="F33">
-        <v>0.001212661231368296</v>
+        <v>0.001212646776464923</v>
       </c>
       <c r="G33">
-        <v>0.001212643396180115</v>
+        <v>0.001212624881407155</v>
       </c>
       <c r="H33">
-        <v>0.001212419372420158</v>
+        <v>0.001212314725717102</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1427,19 +1427,19 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>0.8372471764261157</v>
+        <v>0.7932266244651743</v>
       </c>
       <c r="E36">
-        <v>0.9243268585642836</v>
+        <v>0.9200772634881501</v>
       </c>
       <c r="F36">
-        <v>1.054776021284646</v>
+        <v>1.032354882079403</v>
       </c>
       <c r="G36">
-        <v>1.097921691719676</v>
+        <v>1.088564969979088</v>
       </c>
       <c r="H36">
-        <v>1.182242274776527</v>
+        <v>1.1638479898453</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1473,25 +1473,25 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>5.9164807818077E-09</v>
+        <v>8.717898387874E-09</v>
       </c>
       <c r="C38">
-        <v>2.604551275025311E-09</v>
+        <v>3.843045244721616E-09</v>
       </c>
       <c r="D38">
-        <v>0.09469823105397092</v>
+        <v>0.08890707703568583</v>
       </c>
       <c r="E38">
-        <v>0.1333091182248407</v>
+        <v>0.151206694967806</v>
       </c>
       <c r="F38">
-        <v>0.1543094413352926</v>
+        <v>0.1536698788003086</v>
       </c>
       <c r="G38">
-        <v>0.111164825086564</v>
+        <v>0.1167931797699717</v>
       </c>
       <c r="H38">
-        <v>0.1016768480538353</v>
+        <v>0.1210642434804194</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1525,25 +1525,25 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>3.892749077813031E-08</v>
+        <v>5.749146939689347E-08</v>
       </c>
       <c r="C40">
-        <v>2.260811574527639E-08</v>
+        <v>3.338595076362562E-08</v>
       </c>
       <c r="D40">
-        <v>3.709418107724458E-07</v>
+        <v>7.03277205663201E-07</v>
       </c>
       <c r="E40">
-        <v>1.076742515243804E-06</v>
+        <v>0.01528780081744513</v>
       </c>
       <c r="F40">
-        <v>0.05147782845125809</v>
+        <v>0.1136746289115858</v>
       </c>
       <c r="G40">
-        <v>0.1470104871332872</v>
+        <v>0.2258473032954134</v>
       </c>
       <c r="H40">
-        <v>0.2554986221239938</v>
+        <v>0.3493492899871752</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1551,25 +1551,25 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>3.308836716363262E-08</v>
+        <v>4.886774898915951E-08</v>
       </c>
       <c r="C41">
-        <v>1.921689838570677E-08</v>
+        <v>2.837805815088185E-08</v>
       </c>
       <c r="D41">
-        <v>3.153005391588009E-07</v>
+        <v>5.97785624815521E-07</v>
       </c>
       <c r="E41">
-        <v>9.152311379594557E-07</v>
+        <v>0.01299463069482662</v>
       </c>
       <c r="F41">
-        <v>0.04375615418357275</v>
+        <v>0.09662343457485494</v>
       </c>
       <c r="G41">
-        <v>0.124958914063331</v>
+        <v>0.1919702078010923</v>
       </c>
       <c r="H41">
-        <v>0.217173828805398</v>
+        <v>0.2969468964891022</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1577,25 +1577,25 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>-5.839123614497687E-09</v>
+        <v>-8.623720407733962E-09</v>
       </c>
       <c r="C42">
-        <v>-3.391217359569622E-09</v>
+        <v>-5.007892612743773E-09</v>
       </c>
       <c r="D42">
-        <v>-5.564127161364492E-08</v>
+        <v>-1.0549158084768E-07</v>
       </c>
       <c r="E42">
-        <v>-1.61511377284348E-07</v>
+        <v>-0.002293170122618508</v>
       </c>
       <c r="F42">
-        <v>-0.007721674267685337</v>
+        <v>-0.01705119433673082</v>
       </c>
       <c r="G42">
-        <v>-0.02205157306995614</v>
+        <v>-0.03387709549432108</v>
       </c>
       <c r="H42">
-        <v>-0.03832479331859581</v>
+        <v>-0.05240239349807302</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1609,19 +1609,19 @@
         <v>-0</v>
       </c>
       <c r="D43">
-        <v>-0.5389277082005877</v>
+        <v>-0.531835998235209</v>
       </c>
       <c r="E43">
-        <v>-0.6318907658046181</v>
+        <v>-0.6334628773725092</v>
       </c>
       <c r="F43">
-        <v>-0.6906463759775765</v>
+        <v>-0.658894396596747</v>
       </c>
       <c r="G43">
-        <v>-0.6325751481948266</v>
+        <v>-0.6113911248409071</v>
       </c>
       <c r="H43">
-        <v>-0.560319022702317</v>
+        <v>-0.5275484923739399</v>
       </c>
     </row>
     <row r="44" spans="1:8">
